--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I972"/>
+  <dimension ref="A1:I973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30572,6 +30572,37 @@
       </c>
       <c r="I972" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>5</v>
+      </c>
+      <c r="D973" t="n">
+        <v>6</v>
+      </c>
+      <c r="E973" t="n">
+        <v>17</v>
+      </c>
+      <c r="F973" t="n">
+        <v>34</v>
+      </c>
+      <c r="G973" t="n">
+        <v>36</v>
+      </c>
+      <c r="H973" t="n">
+        <v>3</v>
+      </c>
+      <c r="I973" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -30613,7 +30644,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>11.74</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="3">
@@ -30621,10 +30652,10 @@
         <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>11.33</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="4">
@@ -30635,7 +30666,7 @@
         <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>11.33</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="5">
@@ -30646,7 +30677,7 @@
         <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>11.23</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="6">
@@ -30654,32 +30685,32 @@
         <v>17</v>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>11.12</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
         <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="9">
@@ -30690,7 +30721,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="10">
@@ -30701,7 +30732,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.92</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="11">
@@ -30712,7 +30743,7 @@
         <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="12">
@@ -30723,7 +30754,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="13">
@@ -30734,7 +30765,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="14">
@@ -30745,7 +30776,7 @@
         <v>103</v>
       </c>
       <c r="C14" t="n">
-        <v>10.61</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="15">
@@ -30756,7 +30787,7 @@
         <v>102</v>
       </c>
       <c r="C15" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="16">
@@ -30767,7 +30798,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="17">
@@ -30778,7 +30809,7 @@
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="18">
@@ -30789,7 +30820,7 @@
         <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="19">
@@ -30800,7 +30831,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="20">
@@ -30811,7 +30842,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="21">
@@ -30822,7 +30853,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="22">
@@ -30833,7 +30864,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="23">
@@ -30844,7 +30875,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="24">
@@ -30855,7 +30886,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="25">
@@ -30866,7 +30897,7 @@
         <v>98</v>
       </c>
       <c r="C25" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="26">
@@ -30877,18 +30908,18 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B27" t="n">
         <v>96</v>
       </c>
       <c r="C27" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -30899,18 +30930,18 @@
         <v>96</v>
       </c>
       <c r="C28" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.779999999999999</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -30921,7 +30952,7 @@
         <v>95</v>
       </c>
       <c r="C30" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="31">
@@ -30932,7 +30963,7 @@
         <v>95</v>
       </c>
       <c r="C31" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="32">
@@ -30943,7 +30974,7 @@
         <v>94</v>
       </c>
       <c r="C32" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="33">
@@ -30954,7 +30985,7 @@
         <v>94</v>
       </c>
       <c r="C33" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="34">
@@ -30965,7 +30996,7 @@
         <v>93</v>
       </c>
       <c r="C34" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="35">
@@ -30976,7 +31007,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="36">
@@ -30987,7 +31018,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="37">
@@ -30998,7 +31029,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="38">
@@ -31042,7 +31073,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -31053,7 +31084,7 @@
         <v>89</v>
       </c>
       <c r="C42" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="43">
@@ -31064,7 +31095,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="44">
@@ -31075,7 +31106,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="45">
@@ -31086,29 +31117,29 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B46" t="n">
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="B47" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="48">
@@ -31119,29 +31150,29 @@
         <v>85</v>
       </c>
       <c r="C48" t="n">
-        <v>8.75</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B49" t="n">
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.75</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B50" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.65</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="51">
@@ -31152,7 +31183,7 @@
         <v>77</v>
       </c>
       <c r="C51" t="n">
-        <v>7.93</v>
+        <v>7.92</v>
       </c>
     </row>
   </sheetData>
@@ -31194,7 +31225,7 @@
         <v>208</v>
       </c>
       <c r="C2" t="n">
-        <v>21.42</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="3">
@@ -31202,10 +31233,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="4">
@@ -31216,7 +31247,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.88</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="5">
@@ -31227,7 +31258,7 @@
         <v>187</v>
       </c>
       <c r="C5" t="n">
-        <v>19.26</v>
+        <v>19.24</v>
       </c>
     </row>
     <row r="6">
@@ -31238,7 +31269,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>18.64</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="7">
@@ -31249,7 +31280,7 @@
         <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>18.54</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="8">
@@ -31260,7 +31291,7 @@
         <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>18.13</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="9">
@@ -31271,7 +31302,7 @@
         <v>166</v>
       </c>
       <c r="C9" t="n">
-        <v>17.1</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="10">
@@ -31282,7 +31313,7 @@
         <v>161</v>
       </c>
       <c r="C10" t="n">
-        <v>16.58</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="11">
@@ -31293,7 +31324,7 @@
         <v>146</v>
       </c>
       <c r="C11" t="n">
-        <v>15.04</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="12">
@@ -31312,10 +31343,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.59</v>
+        <v>6.69</v>
       </c>
     </row>
   </sheetData>
@@ -31357,7 +31388,7 @@
         <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>20.27</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="3">
@@ -31365,10 +31396,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.38</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="4">
@@ -31379,7 +31410,7 @@
         <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>18.26</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="5">
@@ -31390,7 +31421,7 @@
         <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>16.93</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="6">
@@ -31401,7 +31432,7 @@
         <v>75</v>
       </c>
       <c r="C6" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="7">
@@ -31412,7 +31443,7 @@
         <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="8">
@@ -31423,7 +31454,7 @@
         <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9">
@@ -31434,7 +31465,7 @@
         <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>16.04</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -31445,7 +31476,7 @@
         <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>15.37</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="11">
@@ -31456,7 +31487,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.92</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="12">
@@ -31467,7 +31498,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>14.48</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="13">
@@ -31475,10 +31506,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.25</v>
+        <v>14.44</v>
       </c>
     </row>
   </sheetData>
@@ -31974,13 +32005,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -31988,13 +32019,13 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>9.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="4">
@@ -32002,13 +32033,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>10.3</v>
       </c>
       <c r="D4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="5">
@@ -32016,13 +32047,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="6">
@@ -32030,13 +32061,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="7">
@@ -32044,13 +32075,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>10.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="8">
@@ -32058,13 +32089,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>10.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="9">
@@ -32072,13 +32103,13 @@
         <v>33</v>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>10.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="10">
@@ -32086,97 +32117,97 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>8.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B15" t="n">
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="D15" t="n">
-        <v>0.95</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B16" t="n">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17">
@@ -32184,46 +32215,46 @@
         <v>47</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>10.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
@@ -32237,27 +32268,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D22" t="n">
         <v>0.89</v>
@@ -32265,72 +32296,72 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="D23" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
@@ -32338,192 +32369,192 @@
         <v>48</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
         <v>12.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>8.9</v>
+        <v>11.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>8.4</v>
+        <v>10.8</v>
       </c>
       <c r="D39" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="D41" t="n">
         <v>0.21</v>
@@ -32531,83 +32562,83 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32615,13 +32646,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>11.3</v>
+        <v>8.9</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32629,13 +32660,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32643,13 +32674,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32657,13 +32688,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I973"/>
+  <dimension ref="A1:I974"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30603,6 +30603,37 @@
       </c>
       <c r="I973" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>6</v>
+      </c>
+      <c r="D974" t="n">
+        <v>21</v>
+      </c>
+      <c r="E974" t="n">
+        <v>31</v>
+      </c>
+      <c r="F974" t="n">
+        <v>47</v>
+      </c>
+      <c r="G974" t="n">
+        <v>48</v>
+      </c>
+      <c r="H974" t="n">
+        <v>2</v>
+      </c>
+      <c r="I974" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -30644,7 +30675,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="3">
@@ -30655,7 +30686,7 @@
         <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="4">
@@ -30666,7 +30697,7 @@
         <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="5">
@@ -30674,10 +30705,10 @@
         <v>21</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>11.21</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="6">
@@ -30688,7 +30719,7 @@
         <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -30699,7 +30730,7 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
@@ -30710,7 +30741,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="9">
@@ -30721,7 +30752,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>11.01</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -30732,7 +30763,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.91</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="11">
@@ -30743,7 +30774,7 @@
         <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="12">
@@ -30754,7 +30785,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30796,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="14">
@@ -30776,7 +30807,7 @@
         <v>103</v>
       </c>
       <c r="C14" t="n">
-        <v>10.6</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="15">
@@ -30787,7 +30818,7 @@
         <v>102</v>
       </c>
       <c r="C15" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="16">
@@ -30798,7 +30829,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="17">
@@ -30809,7 +30840,7 @@
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="18">
@@ -30820,7 +30851,7 @@
         <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="19">
@@ -30831,7 +30862,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="20">
@@ -30842,7 +30873,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="21">
@@ -30853,7 +30884,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="22">
@@ -30864,7 +30895,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="23">
@@ -30875,7 +30906,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.19</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="24">
@@ -30886,7 +30917,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.19</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="25">
@@ -30897,7 +30928,7 @@
         <v>98</v>
       </c>
       <c r="C25" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="26">
@@ -30908,7 +30939,7 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="27">
@@ -30916,10 +30947,10 @@
         <v>6</v>
       </c>
       <c r="B27" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="n">
-        <v>9.880000000000001</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -30930,7 +30961,7 @@
         <v>96</v>
       </c>
       <c r="C28" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -30941,18 +30972,18 @@
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B30" t="n">
         <v>95</v>
       </c>
       <c r="C30" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="31">
@@ -30963,29 +30994,29 @@
         <v>95</v>
       </c>
       <c r="C31" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C32" t="n">
-        <v>9.67</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B33" t="n">
         <v>94</v>
       </c>
       <c r="C33" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="34">
@@ -30996,7 +31027,7 @@
         <v>93</v>
       </c>
       <c r="C34" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="35">
@@ -31007,51 +31038,51 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B36" t="n">
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B37" t="n">
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B38" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="B39" t="n">
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -31062,7 +31093,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31073,7 +31104,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="42">
@@ -31084,7 +31115,7 @@
         <v>89</v>
       </c>
       <c r="C42" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="43">
@@ -31095,7 +31126,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="44">
@@ -31106,7 +31137,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="45">
@@ -31117,7 +31148,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="46">
@@ -31128,7 +31159,7 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="47">
@@ -31139,7 +31170,7 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="48">
@@ -31180,10 +31211,10 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.92</v>
+        <v>8.02</v>
       </c>
     </row>
   </sheetData>
@@ -31225,7 +31256,7 @@
         <v>208</v>
       </c>
       <c r="C2" t="n">
-        <v>21.4</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="3">
@@ -31236,7 +31267,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.47</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="4">
@@ -31247,7 +31278,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.86</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="5">
@@ -31258,7 +31289,7 @@
         <v>187</v>
       </c>
       <c r="C5" t="n">
-        <v>19.24</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="6">
@@ -31269,7 +31300,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>18.62</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="7">
@@ -31280,7 +31311,7 @@
         <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>18.52</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="8">
@@ -31291,7 +31322,7 @@
         <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>18.11</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="9">
@@ -31299,10 +31330,10 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.08</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="10">
@@ -31310,10 +31341,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.56</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="11">
@@ -31324,7 +31355,7 @@
         <v>146</v>
       </c>
       <c r="C11" t="n">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="12">
@@ -31335,7 +31366,7 @@
         <v>82</v>
       </c>
       <c r="C12" t="n">
-        <v>8.44</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="13">
@@ -31346,7 +31377,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.69</v>
+        <v>6.68</v>
       </c>
     </row>
   </sheetData>
@@ -31388,7 +31419,7 @@
         <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>20.22</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="3">
@@ -31399,7 +31430,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.56</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="4">
@@ -31410,7 +31441,7 @@
         <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>18.22</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="5">
@@ -31421,7 +31452,7 @@
         <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>16.89</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="6">
@@ -31432,7 +31463,7 @@
         <v>75</v>
       </c>
       <c r="C6" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="7">
@@ -31443,7 +31474,7 @@
         <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="8">
@@ -31454,7 +31485,7 @@
         <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="9">
@@ -31462,10 +31493,10 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="10">
@@ -31473,10 +31504,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.33</v>
+        <v>15.52</v>
       </c>
     </row>
     <row r="11">
@@ -31487,7 +31518,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.89</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="12">
@@ -31498,7 +31529,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="13">
@@ -31509,7 +31540,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
     </row>
   </sheetData>
@@ -31661,7 +31692,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1 &amp; 18</t>
+          <t>6 &amp; 21</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -31671,7 +31702,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27 &amp; 41</t>
+          <t>1 &amp; 18</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -31681,17 +31712,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>27 &amp; 41</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -31701,7 +31732,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -31711,7 +31742,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -31721,7 +31752,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26 &amp; 49</t>
+          <t>20 &amp; 49</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -31731,7 +31762,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2 &amp; 21</t>
+          <t>26 &amp; 49</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -31741,7 +31772,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11 &amp; 35</t>
+          <t>2 &amp; 21</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -31751,7 +31782,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1 &amp; 47</t>
+          <t>11 &amp; 35</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -31761,7 +31792,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21 &amp; 23</t>
+          <t>1 &amp; 47</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -31771,7 +31802,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6 &amp; 21</t>
+          <t>21 &amp; 23</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32005,13 +32036,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="3">
@@ -32019,27 +32050,27 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>9.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
         <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="5">
@@ -32047,55 +32078,55 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>10.8</v>
+        <v>8.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="9">
@@ -32103,27 +32134,27 @@
         <v>33</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>10.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="11">
@@ -32131,27 +32162,27 @@
         <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>10.3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13">
@@ -32159,220 +32190,220 @@
         <v>38</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>9.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" t="n">
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>0.99</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10.9</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="D28" t="n">
         <v>0.48</v>
@@ -32380,251 +32411,251 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>8.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D30" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="D32" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="D37" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>11.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.6</v>
+        <v>8.9</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="D46" t="n">
         <v>0.09</v>
@@ -32638,7 +32669,7 @@
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32646,13 +32677,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32660,13 +32691,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32674,13 +32705,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32688,13 +32719,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I974"/>
+  <dimension ref="A1:I975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30634,6 +30634,37 @@
       </c>
       <c r="I974" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>4</v>
+      </c>
+      <c r="D975" t="n">
+        <v>8</v>
+      </c>
+      <c r="E975" t="n">
+        <v>10</v>
+      </c>
+      <c r="F975" t="n">
+        <v>17</v>
+      </c>
+      <c r="G975" t="n">
+        <v>37</v>
+      </c>
+      <c r="H975" t="n">
+        <v>5</v>
+      </c>
+      <c r="I975" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -30675,7 +30706,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>11.72</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="3">
@@ -30686,7 +30717,7 @@
         <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>11.41</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="4">
@@ -30697,7 +30728,7 @@
         <v>110</v>
       </c>
       <c r="C4" t="n">
-        <v>11.31</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="5">
@@ -30708,7 +30739,7 @@
         <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>11.31</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="6">
@@ -30716,10 +30747,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="7">
@@ -30730,7 +30761,7 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="8">
@@ -30741,7 +30772,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="9">
@@ -30752,7 +30783,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="10">
@@ -30763,7 +30794,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="11">
@@ -30774,7 +30805,7 @@
         <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="12">
@@ -30785,7 +30816,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="13">
@@ -30796,7 +30827,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="14">
@@ -30807,7 +30838,7 @@
         <v>103</v>
       </c>
       <c r="C14" t="n">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="15">
@@ -30815,10 +30846,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C15" t="n">
-        <v>10.48</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="16">
@@ -30829,7 +30860,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="17">
@@ -30840,18 +30871,18 @@
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.28</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="19">
@@ -30862,7 +30893,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="20">
@@ -30873,29 +30904,29 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B21" t="n">
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B22" t="n">
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="23">
@@ -30906,7 +30937,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="24">
@@ -30917,7 +30948,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="25">
@@ -30928,7 +30959,7 @@
         <v>98</v>
       </c>
       <c r="C25" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="26">
@@ -30939,7 +30970,7 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="27">
@@ -30950,7 +30981,7 @@
         <v>97</v>
       </c>
       <c r="C27" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -30961,7 +30992,7 @@
         <v>96</v>
       </c>
       <c r="C28" t="n">
-        <v>9.869999999999999</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -30972,7 +31003,7 @@
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.869999999999999</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -30983,7 +31014,7 @@
         <v>95</v>
       </c>
       <c r="C30" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="31">
@@ -30994,29 +31025,29 @@
         <v>95</v>
       </c>
       <c r="C31" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="B32" t="n">
         <v>95</v>
       </c>
       <c r="C32" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.66</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="34">
@@ -31027,7 +31058,7 @@
         <v>93</v>
       </c>
       <c r="C34" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31038,7 +31069,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -31049,7 +31080,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -31060,7 +31091,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31071,7 +31102,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31082,7 +31113,7 @@
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -31093,7 +31124,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -31104,29 +31135,29 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B42" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C42" t="n">
-        <v>9.15</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B43" t="n">
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -31137,7 +31168,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -31148,7 +31179,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="46">
@@ -31159,7 +31190,7 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="47">
@@ -31170,7 +31201,7 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="48">
@@ -31181,7 +31212,7 @@
         <v>85</v>
       </c>
       <c r="C48" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="49">
@@ -31192,7 +31223,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="50">
@@ -31203,7 +31234,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="51">
@@ -31214,7 +31245,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>8.02</v>
+        <v>8.01</v>
       </c>
     </row>
   </sheetData>
@@ -31253,10 +31284,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C2" t="n">
-        <v>21.38</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="3">
@@ -31267,7 +31298,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.45</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="4">
@@ -31278,7 +31309,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.84</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="5">
@@ -31286,10 +31317,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" t="n">
-        <v>19.22</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="6">
@@ -31300,7 +31331,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>18.6</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="7">
@@ -31311,7 +31342,7 @@
         <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>18.5</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="8">
@@ -31322,7 +31353,7 @@
         <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>18.09</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="9">
@@ -31333,7 +31364,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.16</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="10">
@@ -31344,7 +31375,7 @@
         <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.65</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="11">
@@ -31355,7 +31386,7 @@
         <v>146</v>
       </c>
       <c r="C11" t="n">
-        <v>15.01</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="12">
@@ -31366,7 +31397,7 @@
         <v>82</v>
       </c>
       <c r="C12" t="n">
-        <v>8.43</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="13">
@@ -31377,7 +31408,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.68</v>
+        <v>6.67</v>
       </c>
     </row>
   </sheetData>
@@ -31416,10 +31447,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" t="n">
-        <v>20.18</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="3">
@@ -31430,7 +31461,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.51</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="4">
@@ -31441,40 +31472,40 @@
         <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>18.18</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
         <v>76</v>
       </c>
       <c r="C5" t="n">
-        <v>16.85</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>16.63</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>16.63</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="8">
@@ -31485,7 +31516,7 @@
         <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>16.63</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="9">
@@ -31496,7 +31527,7 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16.19</v>
+        <v>16.15</v>
       </c>
     </row>
     <row r="10">
@@ -31507,7 +31538,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.52</v>
+        <v>15.49</v>
       </c>
     </row>
     <row r="11">
@@ -31518,7 +31549,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.86</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="12">
@@ -31529,7 +31560,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="13">
@@ -31540,7 +31571,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
     </row>
   </sheetData>
@@ -32033,189 +32064,189 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="D2" t="n">
-        <v>4.11</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B5" t="n">
         <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B15" t="n">
         <v>11</v>
@@ -32229,447 +32260,447 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B16" t="n">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>0.99</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10.9</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
         <v>11.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>8.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.49</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="D32" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.9</v>
+        <v>12.4</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32677,13 +32708,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32691,13 +32722,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32705,13 +32736,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>12.4</v>
+        <v>9.5</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32719,13 +32750,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I975"/>
+  <dimension ref="A1:I976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30665,6 +30665,37 @@
       </c>
       <c r="I975" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>4</v>
+      </c>
+      <c r="D976" t="n">
+        <v>6</v>
+      </c>
+      <c r="E976" t="n">
+        <v>8</v>
+      </c>
+      <c r="F976" t="n">
+        <v>17</v>
+      </c>
+      <c r="G976" t="n">
+        <v>22</v>
+      </c>
+      <c r="H976" t="n">
+        <v>7</v>
+      </c>
+      <c r="I976" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -30706,29 +30737,29 @@
         <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>11.7</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B3" t="n">
         <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.29</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="5">
@@ -30739,18 +30770,18 @@
         <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>11.29</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B6" t="n">
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.29</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="7">
@@ -30761,7 +30792,7 @@
         <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="8">
@@ -30772,7 +30803,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="9">
@@ -30783,7 +30814,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.99</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="10">
@@ -30794,18 +30825,18 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
         <v>104</v>
       </c>
       <c r="C11" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="12">
@@ -30816,7 +30847,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="13">
@@ -30827,29 +30858,29 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>10.57</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B15" t="n">
         <v>103</v>
       </c>
       <c r="C15" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="16">
@@ -30860,7 +30891,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="17">
@@ -30871,7 +30902,7 @@
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="18">
@@ -30882,7 +30913,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.37</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="19">
@@ -30893,7 +30924,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="20">
@@ -30904,7 +30935,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="21">
@@ -30915,7 +30946,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="22">
@@ -30926,7 +30957,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="23">
@@ -30937,7 +30968,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="24">
@@ -30948,7 +30979,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="25">
@@ -30959,40 +30990,40 @@
         <v>98</v>
       </c>
       <c r="C25" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B26" t="n">
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="B27" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>9.960000000000001</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="B28" t="n">
         <v>96</v>
       </c>
       <c r="C28" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="29">
@@ -31003,40 +31034,40 @@
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B30" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.75</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.75</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B32" t="n">
         <v>95</v>
       </c>
       <c r="C32" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="33">
@@ -31047,7 +31078,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="34">
@@ -31058,7 +31089,7 @@
         <v>93</v>
       </c>
       <c r="C34" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -31069,7 +31100,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -31080,7 +31111,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -31091,7 +31122,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -31102,7 +31133,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -31113,7 +31144,7 @@
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="40">
@@ -31124,7 +31155,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="41">
@@ -31135,7 +31166,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="42">
@@ -31146,7 +31177,7 @@
         <v>90</v>
       </c>
       <c r="C42" t="n">
-        <v>9.24</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="43">
@@ -31157,7 +31188,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -31168,7 +31199,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -31179,7 +31210,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="46">
@@ -31190,7 +31221,7 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="47">
@@ -31201,7 +31232,7 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="48">
@@ -31212,7 +31243,7 @@
         <v>85</v>
       </c>
       <c r="C48" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -31223,7 +31254,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -31234,7 +31265,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -31245,7 +31276,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -31287,7 +31318,7 @@
         <v>209</v>
       </c>
       <c r="C2" t="n">
-        <v>21.46</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="3">
@@ -31298,7 +31329,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.43</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="4">
@@ -31309,7 +31340,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.82</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="5">
@@ -31317,10 +31348,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C5" t="n">
-        <v>19.3</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="6">
@@ -31331,7 +31362,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>18.58</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="7">
@@ -31342,7 +31373,7 @@
         <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>18.48</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="8">
@@ -31353,7 +31384,7 @@
         <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>18.07</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="9">
@@ -31364,7 +31395,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.15</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="10">
@@ -31375,7 +31406,7 @@
         <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.63</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="11">
@@ -31383,10 +31414,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.99</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="12">
@@ -31397,7 +31428,7 @@
         <v>82</v>
       </c>
       <c r="C12" t="n">
-        <v>8.42</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="13">
@@ -31450,7 +31481,7 @@
         <v>92</v>
       </c>
       <c r="C2" t="n">
-        <v>20.35</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="3">
@@ -31461,7 +31492,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.47</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="4">
@@ -31472,7 +31503,7 @@
         <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>18.14</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="5">
@@ -31480,32 +31511,32 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>16.81</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="n">
         <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>16.59</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="8">
@@ -31516,7 +31547,7 @@
         <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>16.59</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="9">
@@ -31527,7 +31558,7 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16.15</v>
+        <v>16.11</v>
       </c>
     </row>
     <row r="10">
@@ -31538,7 +31569,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.49</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="11">
@@ -31549,7 +31580,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.82</v>
+        <v>14.79</v>
       </c>
     </row>
     <row r="12">
@@ -31560,7 +31591,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>14.38</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="13">
@@ -31571,7 +31602,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.38</v>
+        <v>14.35</v>
       </c>
     </row>
   </sheetData>
@@ -32067,13 +32098,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>9.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="3">
@@ -32081,13 +32112,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -32095,13 +32126,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>9.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
@@ -32109,13 +32140,13 @@
         <v>32</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="6">
@@ -32123,13 +32154,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7">
@@ -32137,13 +32168,13 @@
         <v>33</v>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>10.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="8">
@@ -32151,13 +32182,13 @@
         <v>49</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
@@ -32165,13 +32196,13 @@
         <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>10.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="10">
@@ -32179,13 +32210,13 @@
         <v>40</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>10.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="11">
@@ -32193,13 +32224,13 @@
         <v>38</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>9.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12">
@@ -32207,41 +32238,41 @@
         <v>23</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>9.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -32249,97 +32280,97 @@
         <v>2</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>10.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B17" t="n">
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="D18" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D19" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="22">
@@ -32347,27 +32378,27 @@
         <v>35</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -32375,27 +32406,27 @@
         <v>50</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
         <v>11.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="26">
@@ -32403,27 +32434,27 @@
         <v>19</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
         <v>9.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0.61</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="28">
@@ -32431,41 +32462,41 @@
         <v>9</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
         <v>9.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="31">
@@ -32473,41 +32504,41 @@
         <v>41</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>9.4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="D33" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="34">
@@ -32515,13 +32546,13 @@
         <v>13</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
         <v>9.6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="35">
@@ -32529,164 +32560,164 @@
         <v>25</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>11.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>8.800000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="D40" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="D45" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D46" t="n">
         <v>0.1</v>
@@ -32694,13 +32725,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.9</v>
+        <v>9.5</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32714,7 +32745,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32728,7 +32759,7 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32736,13 +32767,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32750,13 +32781,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I976"/>
+  <dimension ref="A1:I977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30696,6 +30696,37 @@
       </c>
       <c r="I976" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>11</v>
+      </c>
+      <c r="D977" t="n">
+        <v>25</v>
+      </c>
+      <c r="E977" t="n">
+        <v>40</v>
+      </c>
+      <c r="F977" t="n">
+        <v>41</v>
+      </c>
+      <c r="G977" t="n">
+        <v>45</v>
+      </c>
+      <c r="H977" t="n">
+        <v>1</v>
+      </c>
+      <c r="I977" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -30737,7 +30768,7 @@
         <v>114</v>
       </c>
       <c r="C2" t="n">
-        <v>11.69</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="3">
@@ -30748,7 +30779,7 @@
         <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="4">
@@ -30759,7 +30790,7 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="5">
@@ -30770,7 +30801,7 @@
         <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>11.28</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="6">
@@ -30781,7 +30812,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.28</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="7">
@@ -30789,10 +30820,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>11.08</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="8">
@@ -30803,7 +30834,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.08</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="9">
@@ -30814,7 +30845,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="10">
@@ -30825,29 +30856,29 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.87</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>10.67</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="13">
@@ -30858,7 +30889,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="14">
@@ -30869,7 +30900,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="15">
@@ -30880,7 +30911,7 @@
         <v>103</v>
       </c>
       <c r="C15" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="16">
@@ -30891,7 +30922,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="17">
@@ -30902,7 +30933,7 @@
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="18">
@@ -30913,7 +30944,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="19">
@@ -30924,7 +30955,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="20">
@@ -30935,7 +30966,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="21">
@@ -30946,7 +30977,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="22">
@@ -30957,40 +30988,40 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.05</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="26">
@@ -31001,7 +31032,7 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="27">
@@ -31012,7 +31043,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="28">
@@ -31023,7 +31054,7 @@
         <v>96</v>
       </c>
       <c r="C28" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="29">
@@ -31034,7 +31065,7 @@
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="30">
@@ -31045,7 +31076,7 @@
         <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="31">
@@ -31056,7 +31087,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="32">
@@ -31067,7 +31098,7 @@
         <v>95</v>
       </c>
       <c r="C32" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="33">
@@ -31078,7 +31109,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="34">
@@ -31086,10 +31117,10 @@
         <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" t="n">
-        <v>9.539999999999999</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31100,7 +31131,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -31111,7 +31142,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -31122,7 +31153,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -31133,7 +31164,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -31144,7 +31175,7 @@
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="40">
@@ -31155,7 +31186,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="41">
@@ -31166,7 +31197,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="42">
@@ -31177,7 +31208,7 @@
         <v>90</v>
       </c>
       <c r="C42" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -31188,7 +31219,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.130000000000001</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -31199,7 +31230,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.130000000000001</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -31210,7 +31241,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="46">
@@ -31221,29 +31252,29 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B47" t="n">
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>8.720000000000001</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="49">
@@ -31254,7 +31285,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -31265,7 +31296,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -31276,7 +31307,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
     </row>
   </sheetData>
@@ -31315,10 +31346,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>21.44</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="3">
@@ -31329,7 +31360,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.41</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="4">
@@ -31340,7 +31371,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.79</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="5">
@@ -31351,7 +31382,7 @@
         <v>189</v>
       </c>
       <c r="C5" t="n">
-        <v>19.38</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="6">
@@ -31362,7 +31393,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="n">
-        <v>18.56</v>
+        <v>18.55</v>
       </c>
     </row>
     <row r="7">
@@ -31373,7 +31404,7 @@
         <v>180</v>
       </c>
       <c r="C7" t="n">
-        <v>18.46</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="8">
@@ -31381,10 +31412,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>18.05</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="9">
@@ -31395,7 +31426,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.13</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="10">
@@ -31406,7 +31437,7 @@
         <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.62</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="11">
@@ -31417,7 +31448,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>15.08</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="12">
@@ -31428,7 +31459,7 @@
         <v>82</v>
       </c>
       <c r="C12" t="n">
-        <v>8.41</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="13">
@@ -31439,7 +31470,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.67</v>
+        <v>6.66</v>
       </c>
     </row>
   </sheetData>
@@ -31478,10 +31509,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>20.31</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="3">
@@ -31492,7 +31523,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.43</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="4">
@@ -31503,7 +31534,7 @@
         <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>18.1</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="5">
@@ -31514,7 +31545,7 @@
         <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="6">
@@ -31525,7 +31556,7 @@
         <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>16.78</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="7">
@@ -31536,7 +31567,7 @@
         <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>16.78</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="8">
@@ -31544,10 +31575,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.56</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="9">
@@ -31558,7 +31589,7 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16.11</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="10">
@@ -31569,7 +31600,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.45</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="11">
@@ -31580,7 +31611,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.79</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="12">
@@ -31591,7 +31622,7 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="13">
@@ -31602,7 +31633,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
     </row>
   </sheetData>
@@ -31784,7 +31815,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -31794,7 +31825,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -31804,7 +31835,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -31814,7 +31845,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -31824,7 +31855,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26 &amp; 49</t>
+          <t>20 &amp; 49</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -31834,7 +31865,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2 &amp; 21</t>
+          <t>26 &amp; 49</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -31844,7 +31875,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11 &amp; 35</t>
+          <t>2 &amp; 21</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -31854,7 +31885,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1 &amp; 47</t>
+          <t>11 &amp; 35</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -31864,7 +31895,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21 &amp; 23</t>
+          <t>1 &amp; 47</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -31874,7 +31905,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2 &amp; 30</t>
+          <t>21 &amp; 23</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32098,13 +32129,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
         <v>9.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="3">
@@ -32112,13 +32143,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="4">
@@ -32126,13 +32157,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>9.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="5">
@@ -32140,41 +32171,41 @@
         <v>32</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B7" t="n">
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
@@ -32182,102 +32213,102 @@
         <v>49</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B9" t="n">
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B15" t="n">
         <v>12</v>
@@ -32291,184 +32322,184 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B16" t="n">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B19" t="n">
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>10.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B22" t="n">
         <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>8.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D24" t="n">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>8.4</v>
+        <v>10.8</v>
       </c>
       <c r="D27" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="29">
@@ -32476,94 +32507,94 @@
         <v>46</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="D34" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="D35" t="n">
         <v>0.35</v>
@@ -32571,55 +32602,55 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="D39" t="n">
         <v>0.34</v>
@@ -32627,97 +32658,97 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>11.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="D42" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>12.4</v>
+        <v>9.9</v>
       </c>
       <c r="D44" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D46" t="n">
         <v>0.1</v>
@@ -32725,13 +32756,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32739,13 +32770,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32753,13 +32784,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32767,13 +32798,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32781,13 +32812,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I977"/>
+  <dimension ref="A1:I978"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30727,6 +30727,37 @@
       </c>
       <c r="I977" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>4</v>
+      </c>
+      <c r="D978" t="n">
+        <v>10</v>
+      </c>
+      <c r="E978" t="n">
+        <v>20</v>
+      </c>
+      <c r="F978" t="n">
+        <v>40</v>
+      </c>
+      <c r="G978" t="n">
+        <v>41</v>
+      </c>
+      <c r="H978" t="n">
+        <v>4</v>
+      </c>
+      <c r="I978" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -30765,10 +30796,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.68</v>
+        <v>11.77</v>
       </c>
     </row>
     <row r="3">
@@ -30779,7 +30810,7 @@
         <v>111</v>
       </c>
       <c r="C3" t="n">
-        <v>11.37</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="4">
@@ -30790,7 +30821,7 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.37</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="5">
@@ -30801,7 +30832,7 @@
         <v>110</v>
       </c>
       <c r="C5" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="6">
@@ -30812,7 +30843,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="7">
@@ -30823,7 +30854,7 @@
         <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="8">
@@ -30834,7 +30865,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.07</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="9">
@@ -30845,7 +30876,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.96</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="10">
@@ -30856,7 +30887,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.86</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="11">
@@ -30864,10 +30895,10 @@
         <v>41</v>
       </c>
       <c r="B11" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.76</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="12">
@@ -30878,7 +30909,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="13">
@@ -30889,7 +30920,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="14">
@@ -30900,7 +30931,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="15">
@@ -30911,7 +30942,7 @@
         <v>103</v>
       </c>
       <c r="C15" t="n">
-        <v>10.55</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="16">
@@ -30922,7 +30953,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="17">
@@ -30933,7 +30964,7 @@
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="18">
@@ -30944,7 +30975,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.35</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="19">
@@ -30955,7 +30986,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="20">
@@ -30966,7 +30997,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="21">
@@ -30977,7 +31008,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="22">
@@ -30988,7 +31019,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="23">
@@ -30999,7 +31030,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="24">
@@ -31010,7 +31041,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="25">
@@ -31021,7 +31052,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="26">
@@ -31032,7 +31063,7 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="27">
@@ -31043,7 +31074,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="28">
@@ -31051,10 +31082,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" t="n">
-        <v>9.84</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="29">
@@ -31065,7 +31096,7 @@
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="30">
@@ -31076,7 +31107,7 @@
         <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="31">
@@ -31087,7 +31118,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="32">
@@ -31098,7 +31129,7 @@
         <v>95</v>
       </c>
       <c r="C32" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -31109,7 +31140,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -31117,10 +31148,10 @@
         <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.630000000000001</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31131,7 +31162,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="36">
@@ -31142,7 +31173,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="37">
@@ -31153,7 +31184,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="38">
@@ -31164,7 +31195,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="39">
@@ -31175,7 +31206,7 @@
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="40">
@@ -31186,29 +31217,29 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B41" t="n">
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B42" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.220000000000001</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="43">
@@ -31219,7 +31250,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -31230,7 +31261,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -31241,7 +31272,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="46">
@@ -31252,7 +31283,7 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -31263,7 +31294,7 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -31274,7 +31305,7 @@
         <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -31285,7 +31316,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.710000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -31296,7 +31327,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.710000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -31307,7 +31338,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
     </row>
   </sheetData>
@@ -31349,7 +31380,7 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>21.52</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="3">
@@ -31360,7 +31391,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="4">
@@ -31371,7 +31402,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.77</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="5">
@@ -31382,7 +31413,7 @@
         <v>189</v>
       </c>
       <c r="C5" t="n">
-        <v>19.36</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="6">
@@ -31390,10 +31421,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>18.55</v>
+        <v>18.63</v>
       </c>
     </row>
     <row r="7">
@@ -31401,10 +31432,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>18.44</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="8">
@@ -31415,7 +31446,7 @@
         <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="9">
@@ -31426,7 +31457,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.11</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="10">
@@ -31437,7 +31468,7 @@
         <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.6</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="11">
@@ -31448,7 +31479,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>15.06</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="12">
@@ -31459,7 +31490,7 @@
         <v>82</v>
       </c>
       <c r="C12" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -31470,7 +31501,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
     </row>
   </sheetData>
@@ -31512,7 +31543,7 @@
         <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>20.48</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="3">
@@ -31523,7 +31554,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.38</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="4">
@@ -31534,7 +31565,7 @@
         <v>82</v>
       </c>
       <c r="C4" t="n">
-        <v>18.06</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="5">
@@ -31545,29 +31576,29 @@
         <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>16.96</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="n">
-        <v>16.74</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>16.74</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="8">
@@ -31578,7 +31609,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.74</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="9">
@@ -31589,7 +31620,7 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16.08</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="10">
@@ -31600,7 +31631,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.42</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="11">
@@ -31611,7 +31642,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.76</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="12">
@@ -31619,10 +31650,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>14.32</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="13">
@@ -31633,7 +31664,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.32</v>
+        <v>14.29</v>
       </c>
     </row>
   </sheetData>
@@ -32129,13 +32160,13 @@
         <v>30</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>9.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -32143,13 +32174,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="4">
@@ -32157,13 +32188,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>9.6</v>
       </c>
       <c r="D4" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="5">
@@ -32171,13 +32202,13 @@
         <v>32</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="6">
@@ -32185,13 +32216,13 @@
         <v>33</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>10.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="7">
@@ -32199,13 +32230,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>10.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="8">
@@ -32213,13 +32244,13 @@
         <v>49</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -32227,13 +32258,13 @@
         <v>38</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>9.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="10">
@@ -32241,13 +32272,13 @@
         <v>23</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
@@ -32255,13 +32286,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="12">
@@ -32269,13 +32300,13 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="13">
@@ -32283,13 +32314,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>9.6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="14">
@@ -32297,13 +32328,13 @@
         <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>10.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="15">
@@ -32311,13 +32342,13 @@
         <v>29</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>10.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="16">
@@ -32325,13 +32356,13 @@
         <v>26</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>10.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="17">
@@ -32339,13 +32370,13 @@
         <v>27</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>11.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.89</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="18">
@@ -32353,13 +32384,13 @@
         <v>43</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>10.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="19">
@@ -32367,13 +32398,13 @@
         <v>35</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="20">
@@ -32381,13 +32412,13 @@
         <v>39</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>9.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21">
@@ -32395,13 +32426,13 @@
         <v>50</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
         <v>11.2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -32409,13 +32440,13 @@
         <v>12</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
         <v>10.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="23">
@@ -32423,13 +32454,13 @@
         <v>44</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
         <v>10.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="24">
@@ -32437,13 +32468,13 @@
         <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
         <v>9.9</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="25">
@@ -32451,27 +32482,27 @@
         <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
         <v>9.6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="27">
@@ -32479,13 +32510,13 @@
         <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
         <v>10.8</v>
       </c>
       <c r="D27" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="28">
@@ -32493,83 +32524,83 @@
         <v>16</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
         <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>11.3</v>
+        <v>9.6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.44</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="34">
@@ -32577,94 +32608,94 @@
         <v>5</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
         <v>11.4</v>
       </c>
       <c r="D34" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="D35" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>10.3</v>
+        <v>12.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.24</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D38" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D40" t="n">
         <v>0.21</v>
@@ -32672,49 +32703,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
@@ -32728,41 +32759,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32770,13 +32801,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32784,13 +32815,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32812,13 +32843,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I978"/>
+  <dimension ref="A1:I979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30758,6 +30758,37 @@
       </c>
       <c r="I978" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>3</v>
+      </c>
+      <c r="D979" t="n">
+        <v>17</v>
+      </c>
+      <c r="E979" t="n">
+        <v>30</v>
+      </c>
+      <c r="F979" t="n">
+        <v>35</v>
+      </c>
+      <c r="G979" t="n">
+        <v>43</v>
+      </c>
+      <c r="H979" t="n">
+        <v>1</v>
+      </c>
+      <c r="I979" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -30799,7 +30830,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.77</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="3">
@@ -30807,10 +30838,10 @@
         <v>17</v>
       </c>
       <c r="B3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.36</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="4">
@@ -30821,29 +30852,29 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.36</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>11.26</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.26</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="7">
@@ -30854,7 +30885,7 @@
         <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>11.16</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="8">
@@ -30865,7 +30896,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="9">
@@ -30876,7 +30907,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.95</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="10">
@@ -30887,7 +30918,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="11">
@@ -30898,7 +30929,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="12">
@@ -30909,7 +30940,7 @@
         <v>104</v>
       </c>
       <c r="C12" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="13">
@@ -30920,7 +30951,7 @@
         <v>104</v>
       </c>
       <c r="C13" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="14">
@@ -30931,40 +30962,40 @@
         <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B15" t="n">
         <v>103</v>
       </c>
       <c r="C15" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B16" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.44</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
         <v>102</v>
       </c>
       <c r="C17" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="18">
@@ -30975,7 +31006,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.34</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="19">
@@ -30986,7 +31017,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="20">
@@ -30997,7 +31028,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="21">
@@ -31008,7 +31039,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="22">
@@ -31019,7 +31050,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="23">
@@ -31030,7 +31061,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="24">
@@ -31041,7 +31072,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="25">
@@ -31052,7 +31083,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="26">
@@ -31063,7 +31094,7 @@
         <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="27">
@@ -31074,7 +31105,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="28">
@@ -31085,18 +31116,18 @@
         <v>97</v>
       </c>
       <c r="C28" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="30">
@@ -31107,7 +31138,7 @@
         <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="31">
@@ -31118,29 +31149,29 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B32" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.720000000000001</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B33" t="n">
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -31151,7 +31182,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31162,7 +31193,7 @@
         <v>93</v>
       </c>
       <c r="C35" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="36">
@@ -31173,7 +31204,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="37">
@@ -31184,29 +31215,29 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B38" t="n">
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B39" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.42</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="40">
@@ -31217,7 +31248,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="41">
@@ -31228,7 +31259,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -31239,7 +31270,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -31250,7 +31281,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="44">
@@ -31261,7 +31292,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="45">
@@ -31283,7 +31314,7 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -31294,7 +31325,7 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -31305,7 +31336,7 @@
         <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -31316,7 +31347,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="50">
@@ -31327,7 +31358,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="51">
@@ -31380,7 +31411,7 @@
         <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>21.49</v>
+        <v>21.47</v>
       </c>
     </row>
     <row r="3">
@@ -31391,7 +31422,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.37</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="4">
@@ -31402,7 +31433,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.75</v>
+        <v>19.73</v>
       </c>
     </row>
     <row r="5">
@@ -31413,7 +31444,7 @@
         <v>189</v>
       </c>
       <c r="C5" t="n">
-        <v>19.34</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="6">
@@ -31424,7 +31455,7 @@
         <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>18.63</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="7">
@@ -31435,7 +31466,7 @@
         <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>18.53</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="8">
@@ -31443,10 +31474,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.12</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="9">
@@ -31457,7 +31488,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.09</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="10">
@@ -31468,7 +31499,7 @@
         <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.58</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="11">
@@ -31479,7 +31510,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>15.05</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="12">
@@ -31487,10 +31518,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.390000000000001</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="13">
@@ -31543,7 +31574,7 @@
         <v>93</v>
       </c>
       <c r="C2" t="n">
-        <v>20.44</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="3">
@@ -31554,7 +31585,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.34</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="4">
@@ -31562,54 +31593,54 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18.02</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>77</v>
       </c>
       <c r="C5" t="n">
-        <v>16.92</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
         <v>77</v>
       </c>
       <c r="C6" t="n">
-        <v>16.92</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.7</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9">
@@ -31620,7 +31651,7 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16.04</v>
+        <v>16.01</v>
       </c>
     </row>
     <row r="10">
@@ -31631,7 +31662,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.38</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="11">
@@ -31642,7 +31673,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.73</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="12">
@@ -31653,7 +31684,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>14.51</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="13">
@@ -31664,7 +31695,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.29</v>
+        <v>14.25</v>
       </c>
     </row>
   </sheetData>
@@ -31926,7 +31957,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1 &amp; 47</t>
+          <t>30 &amp; 43</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -31936,7 +31967,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21 &amp; 23</t>
+          <t>1 &amp; 47</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32157,142 +32188,142 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.67</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B4" t="n">
         <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B6" t="n">
         <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="B7" t="n">
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="12">
@@ -32300,32 +32331,32 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B14" t="n">
         <v>14</v>
@@ -32339,41 +32370,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D17" t="n">
         <v>0.98</v>
@@ -32381,181 +32412,181 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D19" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B20" t="n">
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>9.4</v>
+        <v>11.2</v>
       </c>
       <c r="D20" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
         <v>9</v>
       </c>
-      <c r="C23" t="n">
-        <v>10.4</v>
-      </c>
       <c r="D23" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="D24" t="n">
-        <v>0.91</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
         <v>9.6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="D30" t="n">
         <v>0.53</v>
@@ -32563,147 +32594,147 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="D31" t="n">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B34" t="n">
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>12.4</v>
+        <v>9.9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
@@ -32717,83 +32748,83 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>11.3</v>
+        <v>8.4</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32801,13 +32832,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32815,13 +32846,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32829,13 +32860,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32843,13 +32874,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I979"/>
+  <dimension ref="A1:I980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30789,6 +30789,37 @@
       </c>
       <c r="I979" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>1</v>
+      </c>
+      <c r="D980" t="n">
+        <v>3</v>
+      </c>
+      <c r="E980" t="n">
+        <v>6</v>
+      </c>
+      <c r="F980" t="n">
+        <v>13</v>
+      </c>
+      <c r="G980" t="n">
+        <v>23</v>
+      </c>
+      <c r="H980" t="n">
+        <v>5</v>
+      </c>
+      <c r="I980" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -30830,7 +30861,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.76</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="3">
@@ -30841,7 +30872,7 @@
         <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.45</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="4">
@@ -30852,7 +30883,7 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.35</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="5">
@@ -30863,7 +30894,7 @@
         <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>11.35</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="6">
@@ -30874,7 +30905,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.25</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="7">
@@ -30885,7 +30916,7 @@
         <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>11.15</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="8">
@@ -30896,7 +30927,7 @@
         <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="9">
@@ -30907,7 +30938,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.94</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="10">
@@ -30918,7 +30949,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="11">
@@ -30929,18 +30960,18 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="13">
@@ -30948,21 +30979,21 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.63</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
         <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="15">
@@ -30973,29 +31004,29 @@
         <v>103</v>
       </c>
       <c r="C15" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
         <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.43</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="18">
@@ -31006,7 +31037,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="19">
@@ -31017,7 +31048,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="20">
@@ -31028,7 +31059,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="21">
@@ -31039,7 +31070,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="22">
@@ -31050,7 +31081,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="23">
@@ -31061,7 +31092,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="24">
@@ -31072,7 +31103,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="25">
@@ -31083,7 +31114,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="26">
@@ -31091,10 +31122,10 @@
         <v>6</v>
       </c>
       <c r="B26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.02</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="27">
@@ -31105,7 +31136,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="28">
@@ -31116,7 +31147,7 @@
         <v>97</v>
       </c>
       <c r="C28" t="n">
-        <v>9.92</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="29">
@@ -31127,7 +31158,7 @@
         <v>96</v>
       </c>
       <c r="C29" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="30">
@@ -31138,7 +31169,7 @@
         <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="31">
@@ -31149,7 +31180,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="32">
@@ -31160,7 +31191,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="33">
@@ -31171,7 +31202,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -31182,18 +31213,18 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.51</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="36">
@@ -31204,7 +31235,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -31215,18 +31246,18 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" t="n">
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="39">
@@ -31237,7 +31268,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="40">
@@ -31248,7 +31279,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="41">
@@ -31281,7 +31312,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="44">
@@ -31292,7 +31323,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="45">
@@ -31303,7 +31334,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -31314,7 +31345,7 @@
         <v>86</v>
       </c>
       <c r="C46" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -31325,7 +31356,7 @@
         <v>86</v>
       </c>
       <c r="C47" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -31336,7 +31367,7 @@
         <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -31347,7 +31378,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="50">
@@ -31358,7 +31389,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="51">
@@ -31369,7 +31400,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.98</v>
+        <v>7.97</v>
       </c>
     </row>
   </sheetData>
@@ -31408,10 +31439,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C2" t="n">
-        <v>21.47</v>
+        <v>21.55</v>
       </c>
     </row>
     <row r="3">
@@ -31422,7 +31453,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="4">
@@ -31433,7 +31464,7 @@
         <v>193</v>
       </c>
       <c r="C4" t="n">
-        <v>19.73</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="5">
@@ -31441,10 +31472,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>19.33</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="6">
@@ -31455,7 +31486,7 @@
         <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>18.61</v>
+        <v>18.59</v>
       </c>
     </row>
     <row r="7">
@@ -31466,7 +31497,7 @@
         <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>18.51</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="8">
@@ -31477,7 +31508,7 @@
         <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.2</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="9">
@@ -31488,7 +31519,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.08</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="10">
@@ -31499,7 +31530,7 @@
         <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>16.56</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="11">
@@ -31510,7 +31541,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>15.03</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="12">
@@ -31521,7 +31552,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.49</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="13">
@@ -31532,7 +31563,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
     </row>
   </sheetData>
@@ -31571,10 +31602,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>20.39</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="3">
@@ -31585,7 +31616,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.3</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="4">
@@ -31596,29 +31627,29 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18.2</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>16.89</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
         <v>77</v>
       </c>
       <c r="C6" t="n">
-        <v>16.89</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="7">
@@ -31629,7 +31660,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.89</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="8">
@@ -31640,7 +31671,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="9">
@@ -31651,7 +31682,7 @@
         <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>16.01</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="10">
@@ -31662,7 +31693,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.35</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="11">
@@ -31673,7 +31704,7 @@
         <v>67</v>
       </c>
       <c r="C11" t="n">
-        <v>14.69</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="12">
@@ -31684,7 +31715,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>14.47</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="13">
@@ -31695,7 +31726,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.25</v>
+        <v>14.22</v>
       </c>
     </row>
   </sheetData>
@@ -32191,13 +32222,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="3">
@@ -32205,13 +32236,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>9.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -32219,13 +32250,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>10.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="5">
@@ -32233,13 +32264,13 @@
         <v>33</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="6">
@@ -32247,13 +32278,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="7">
@@ -32261,150 +32292,150 @@
         <v>38</v>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>9.1</v>
+        <v>9.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>10.2</v>
+        <v>11.2</v>
       </c>
       <c r="D17" t="n">
         <v>0.98</v>
@@ -32415,256 +32446,256 @@
         <v>44</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>10.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>11.2</v>
+        <v>10.8</v>
       </c>
       <c r="D20" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>10.8</v>
+        <v>11.3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>8.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="D30" t="n">
-        <v>0.53</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>12.4</v>
+        <v>10.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>0.41</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
@@ -32678,69 +32709,69 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10.1</v>
+        <v>8.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="D41" t="n">
         <v>0.2</v>
@@ -32748,41 +32779,41 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D44" t="n">
         <v>0.11</v>
@@ -32790,27 +32821,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D46" t="n">
         <v>0.1</v>
@@ -32818,13 +32849,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.4</v>
+        <v>9.1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32832,13 +32863,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32846,13 +32877,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32860,13 +32891,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32874,13 +32905,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I980"/>
+  <dimension ref="A1:I981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30820,6 +30820,37 @@
       </c>
       <c r="I980" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>4</v>
+      </c>
+      <c r="D981" t="n">
+        <v>11</v>
+      </c>
+      <c r="E981" t="n">
+        <v>12</v>
+      </c>
+      <c r="F981" t="n">
+        <v>16</v>
+      </c>
+      <c r="G981" t="n">
+        <v>30</v>
+      </c>
+      <c r="H981" t="n">
+        <v>8</v>
+      </c>
+      <c r="I981" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -30861,7 +30892,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.75</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="3">
@@ -30872,7 +30903,7 @@
         <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.44</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="4">
@@ -30883,7 +30914,7 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.34</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="5">
@@ -30894,7 +30925,7 @@
         <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>11.34</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="6">
@@ -30905,7 +30936,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.24</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="7">
@@ -30913,10 +30944,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.13</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="8">
@@ -30924,10 +30955,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.03</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="9">
@@ -30938,7 +30969,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.93</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="10">
@@ -30949,7 +30980,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="11">
@@ -30960,7 +30991,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="12">
@@ -30971,7 +31002,7 @@
         <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="13">
@@ -30982,29 +31013,29 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B14" t="n">
         <v>104</v>
       </c>
       <c r="C14" t="n">
-        <v>10.62</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.52</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="16">
@@ -31015,7 +31046,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="17">
@@ -31026,7 +31057,7 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="18">
@@ -31037,7 +31068,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="19">
@@ -31048,7 +31079,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="20">
@@ -31059,7 +31090,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="21">
@@ -31070,7 +31101,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="22">
@@ -31081,7 +31112,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="23">
@@ -31092,7 +31123,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="24">
@@ -31103,7 +31134,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="25">
@@ -31114,7 +31145,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="26">
@@ -31125,40 +31156,40 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B28" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.81</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="30">
@@ -31169,7 +31200,7 @@
         <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -31180,18 +31211,18 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -31202,7 +31233,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="34">
@@ -31213,7 +31244,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="35">
@@ -31224,7 +31255,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="36">
@@ -31235,7 +31266,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="37">
@@ -31246,7 +31277,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="38">
@@ -31257,7 +31288,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="39">
@@ -31268,7 +31299,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="40">
@@ -31279,7 +31310,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31290,7 +31321,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.300000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -31301,7 +31332,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.300000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31312,7 +31343,7 @@
         <v>89</v>
       </c>
       <c r="C43" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="44">
@@ -31323,7 +31354,7 @@
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="45">
@@ -31334,7 +31365,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -31378,7 +31409,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="50">
@@ -31389,7 +31420,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="51">
@@ -31400,7 +31431,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.97</v>
+        <v>7.96</v>
       </c>
     </row>
   </sheetData>
@@ -31442,7 +31473,7 @@
         <v>211</v>
       </c>
       <c r="C2" t="n">
-        <v>21.55</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="3">
@@ -31453,7 +31484,7 @@
         <v>199</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="4">
@@ -31461,10 +31492,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4" t="n">
-        <v>19.71</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="5">
@@ -31475,7 +31506,7 @@
         <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>19.41</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="6">
@@ -31486,7 +31517,7 @@
         <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>18.59</v>
+        <v>18.57</v>
       </c>
     </row>
     <row r="7">
@@ -31497,7 +31528,7 @@
         <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>18.49</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="8">
@@ -31508,7 +31539,7 @@
         <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.18</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="9">
@@ -31519,7 +31550,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.06</v>
+        <v>17.04</v>
       </c>
     </row>
     <row r="10">
@@ -31527,10 +31558,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.55</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="11">
@@ -31541,7 +31572,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>15.02</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -31552,7 +31583,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.48</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -31563,7 +31594,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.64</v>
+        <v>6.63</v>
       </c>
     </row>
   </sheetData>
@@ -31605,7 +31636,7 @@
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>20.57</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="3">
@@ -31616,7 +31647,7 @@
         <v>88</v>
       </c>
       <c r="C3" t="n">
-        <v>19.26</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="4">
@@ -31627,7 +31658,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18.16</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="5">
@@ -31638,7 +31669,7 @@
         <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>17.07</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="6">
@@ -31649,7 +31680,7 @@
         <v>77</v>
       </c>
       <c r="C6" t="n">
-        <v>16.85</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="7">
@@ -31660,7 +31691,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.85</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="8">
@@ -31671,7 +31702,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.63</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="9">
@@ -31679,10 +31710,10 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.97</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="10">
@@ -31693,7 +31724,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.32</v>
+        <v>15.28</v>
       </c>
     </row>
     <row r="11">
@@ -31701,10 +31732,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>14.66</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="12">
@@ -31715,7 +31746,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>14.44</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="13">
@@ -31726,7 +31757,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.22</v>
+        <v>14.19</v>
       </c>
     </row>
   </sheetData>
@@ -31768,7 +31799,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17 &amp; 39</t>
+          <t>16 &amp; 30</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -31778,11 +31809,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16 &amp; 30</t>
+          <t>17 &amp; 39</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -32222,13 +32253,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="3">
@@ -32236,13 +32267,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>9.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -32250,13 +32281,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>10.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="5">
@@ -32264,13 +32295,13 @@
         <v>33</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="6">
@@ -32278,13 +32309,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -32292,13 +32323,13 @@
         <v>38</v>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="8">
@@ -32306,13 +32337,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="9">
@@ -32320,13 +32351,13 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="10">
@@ -32334,13 +32365,13 @@
         <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11">
@@ -32348,13 +32379,13 @@
         <v>26</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>10.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="12">
@@ -32362,13 +32393,13 @@
         <v>29</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>10.1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="13">
@@ -32376,13 +32407,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>11.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14">
@@ -32390,27 +32421,27 @@
         <v>39</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>9.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>44</v>
+      </c>
+      <c r="B15" t="n">
         <v>12</v>
       </c>
-      <c r="B15" t="n">
-        <v>11</v>
-      </c>
       <c r="C15" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16">
@@ -32418,13 +32449,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>9.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="17">
@@ -32432,41 +32463,41 @@
         <v>50</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
         <v>11.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B18" t="n">
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="20">
@@ -32474,111 +32505,111 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>10.8</v>
       </c>
       <c r="D20" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B22" t="n">
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>10.6</v>
+        <v>11.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>11.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.61</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0.61</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>8.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="28">
@@ -32586,94 +32617,94 @@
         <v>31</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
         <v>10.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>12.4</v>
+        <v>10.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.49</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="D33" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="D34" t="n">
         <v>0.4</v>
@@ -32681,97 +32712,97 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.9</v>
+        <v>8.4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>10.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="D41" t="n">
         <v>0.2</v>
@@ -32779,55 +32810,55 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D44" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D45" t="n">
         <v>0.1</v>
@@ -32835,27 +32866,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32863,13 +32894,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32877,13 +32908,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32891,13 +32922,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32905,13 +32936,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I981"/>
+  <dimension ref="A1:I982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30851,6 +30851,37 @@
       </c>
       <c r="I981" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>5</v>
+      </c>
+      <c r="D982" t="n">
+        <v>26</v>
+      </c>
+      <c r="E982" t="n">
+        <v>28</v>
+      </c>
+      <c r="F982" t="n">
+        <v>30</v>
+      </c>
+      <c r="G982" t="n">
+        <v>40</v>
+      </c>
+      <c r="H982" t="n">
+        <v>3</v>
+      </c>
+      <c r="I982" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -30892,7 +30923,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.73</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="3">
@@ -30903,7 +30934,7 @@
         <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="4">
@@ -30914,7 +30945,7 @@
         <v>111</v>
       </c>
       <c r="C4" t="n">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="5">
@@ -30925,7 +30956,7 @@
         <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="6">
@@ -30936,7 +30967,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="7">
@@ -30947,7 +30978,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="8">
@@ -30958,7 +30989,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="9">
@@ -30969,7 +31000,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.92</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="10">
@@ -30980,7 +31011,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="11">
@@ -30991,40 +31022,40 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.61</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="15">
@@ -31035,7 +31066,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.61</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="16">
@@ -31046,7 +31077,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17">
@@ -31057,7 +31088,7 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="18">
@@ -31068,7 +31099,7 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="19">
@@ -31079,7 +31110,7 @@
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="20">
@@ -31090,7 +31121,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="21">
@@ -31101,7 +31132,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="22">
@@ -31112,7 +31143,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="23">
@@ -31123,7 +31154,7 @@
         <v>99</v>
       </c>
       <c r="C23" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="24">
@@ -31134,7 +31165,7 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="25">
@@ -31145,7 +31176,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="26">
@@ -31156,7 +31187,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="27">
@@ -31167,7 +31198,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="28">
@@ -31178,7 +31209,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="29">
@@ -31189,7 +31220,7 @@
         <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -31200,7 +31231,7 @@
         <v>96</v>
       </c>
       <c r="C30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -31211,40 +31242,40 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B32" t="n">
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.69</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B34" t="n">
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="35">
@@ -31255,7 +31286,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="36">
@@ -31266,7 +31297,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="37">
@@ -31277,7 +31308,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="38">
@@ -31288,7 +31319,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="39">
@@ -31299,7 +31330,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="40">
@@ -31310,7 +31341,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31321,7 +31352,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -31332,73 +31363,73 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B43" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.08</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B44" t="n">
         <v>89</v>
       </c>
       <c r="C44" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B45" t="n">
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B46" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C46" t="n">
-        <v>8.779999999999999</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B47" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.779999999999999</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B48" t="n">
         <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>8.779999999999999</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="49">
@@ -31409,7 +31440,7 @@
         <v>85</v>
       </c>
       <c r="C49" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="50">
@@ -31420,7 +31451,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="51">
@@ -31431,7 +31462,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.96</v>
+        <v>7.95</v>
       </c>
     </row>
   </sheetData>
@@ -31473,7 +31504,7 @@
         <v>211</v>
       </c>
       <c r="C2" t="n">
-        <v>21.53</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="3">
@@ -31481,10 +31512,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>20.31</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="4">
@@ -31495,7 +31526,7 @@
         <v>194</v>
       </c>
       <c r="C4" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="5">
@@ -31506,7 +31537,7 @@
         <v>190</v>
       </c>
       <c r="C5" t="n">
-        <v>19.39</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="6">
@@ -31514,10 +31545,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>18.57</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="7">
@@ -31528,7 +31559,7 @@
         <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>18.47</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="8">
@@ -31539,7 +31570,7 @@
         <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.16</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="9">
@@ -31550,7 +31581,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.04</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="10">
@@ -31561,7 +31592,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.63</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="11">
@@ -31572,7 +31603,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="12">
@@ -31583,7 +31614,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -31636,7 +31667,7 @@
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>20.52</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="3">
@@ -31644,10 +31675,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>19.21</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="4">
@@ -31658,7 +31689,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="5">
@@ -31669,29 +31700,29 @@
         <v>78</v>
       </c>
       <c r="C5" t="n">
-        <v>17.03</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.81</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
         <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.81</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="8">
@@ -31702,7 +31733,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.59</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="9">
@@ -31713,7 +31744,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>16.16</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="10">
@@ -31724,7 +31755,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.28</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="11">
@@ -31735,7 +31766,7 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>14.85</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="12">
@@ -31746,7 +31777,7 @@
         <v>66</v>
       </c>
       <c r="C12" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="13">
@@ -31757,7 +31788,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.19</v>
+        <v>14.16</v>
       </c>
     </row>
   </sheetData>
@@ -32253,13 +32284,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -32267,13 +32298,13 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
         <v>9.6</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="4">
@@ -32281,13 +32312,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>10.3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5">
@@ -32295,13 +32326,13 @@
         <v>33</v>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6">
@@ -32309,13 +32340,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="7">
@@ -32323,13 +32354,13 @@
         <v>38</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="8">
@@ -32337,13 +32368,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9">
@@ -32351,13 +32382,13 @@
         <v>2</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="10">
@@ -32365,69 +32396,69 @@
         <v>18</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D12" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
@@ -32435,55 +32466,55 @@
         <v>44</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>10.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B17" t="n">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B18" t="n">
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="D18" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="19">
@@ -32491,321 +32522,321 @@
         <v>46</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B22" t="n">
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B25" t="n">
         <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>12.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D30" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>11.3</v>
+        <v>8.4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9.9</v>
+        <v>10.8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>8.4</v>
+        <v>10.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
@@ -32813,38 +32844,38 @@
         <v>13</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>9.5</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="D44" t="n">
         <v>0.1</v>
@@ -32852,27 +32883,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
         <v>0.11</v>
@@ -32880,13 +32911,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32894,13 +32925,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32908,13 +32939,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32922,13 +32953,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32936,13 +32967,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I982"/>
+  <dimension ref="A1:I983"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30882,6 +30882,37 @@
       </c>
       <c r="I982" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>15</v>
+      </c>
+      <c r="D983" t="n">
+        <v>22</v>
+      </c>
+      <c r="E983" t="n">
+        <v>24</v>
+      </c>
+      <c r="F983" t="n">
+        <v>34</v>
+      </c>
+      <c r="G983" t="n">
+        <v>42</v>
+      </c>
+      <c r="H983" t="n">
+        <v>4</v>
+      </c>
+      <c r="I983" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -30923,7 +30954,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.72</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="3">
@@ -30934,7 +30965,7 @@
         <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="4">
@@ -30942,10 +30973,10 @@
         <v>34</v>
       </c>
       <c r="B4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>11.31</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="5">
@@ -30956,7 +30987,7 @@
         <v>111</v>
       </c>
       <c r="C5" t="n">
-        <v>11.31</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="6">
@@ -30967,7 +30998,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -30978,7 +31009,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="8">
@@ -30989,7 +31020,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="9">
@@ -31000,7 +31031,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.91</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="10">
@@ -31011,7 +31042,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.81</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="11">
@@ -31022,7 +31053,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.81</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="12">
@@ -31033,7 +31064,7 @@
         <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="13">
@@ -31044,7 +31075,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="14">
@@ -31055,7 +31086,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="15">
@@ -31066,7 +31097,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.6</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="16">
@@ -31077,7 +31108,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="17">
@@ -31088,7 +31119,7 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="18">
@@ -31099,18 +31130,18 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" t="n">
         <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="20">
@@ -31121,7 +31152,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="21">
@@ -31132,7 +31163,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="22">
@@ -31143,18 +31174,18 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="B23" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>10.09</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="24">
@@ -31165,18 +31196,18 @@
         <v>99</v>
       </c>
       <c r="C24" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B25" t="n">
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="26">
@@ -31187,7 +31218,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="27">
@@ -31198,7 +31229,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="28">
@@ -31209,7 +31240,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="29">
@@ -31220,7 +31251,7 @@
         <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -31228,10 +31259,10 @@
         <v>22</v>
       </c>
       <c r="B30" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.789999999999999</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -31242,7 +31273,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -31253,7 +31284,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -31264,7 +31295,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -31275,7 +31306,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="35">
@@ -31286,7 +31317,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="36">
@@ -31297,7 +31328,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -31308,7 +31339,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31319,7 +31350,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31330,62 +31361,62 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n">
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B41" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.279999999999999</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B42" t="n">
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B43" t="n">
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B44" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.07</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="45">
@@ -31396,7 +31427,7 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -31407,7 +31438,7 @@
         <v>87</v>
       </c>
       <c r="C46" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -31418,7 +31449,7 @@
         <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -31429,7 +31460,7 @@
         <v>86</v>
       </c>
       <c r="C48" t="n">
-        <v>8.77</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="49">
@@ -31462,7 +31493,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.95</v>
+        <v>7.94</v>
       </c>
     </row>
   </sheetData>
@@ -31504,7 +31535,7 @@
         <v>211</v>
       </c>
       <c r="C2" t="n">
-        <v>21.51</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="3">
@@ -31515,7 +31546,7 @@
         <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="4">
@@ -31526,7 +31557,7 @@
         <v>194</v>
       </c>
       <c r="C4" t="n">
-        <v>19.78</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="5">
@@ -31534,10 +31565,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>19.37</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="6">
@@ -31548,7 +31579,7 @@
         <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>18.65</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="7">
@@ -31556,10 +31587,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>18.45</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="8">
@@ -31570,7 +31601,7 @@
         <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.14</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="9">
@@ -31581,7 +31612,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.02</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="10">
@@ -31592,7 +31623,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.62</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="11">
@@ -31603,7 +31634,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.98</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="12">
@@ -31614,7 +31645,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -31625,7 +31656,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.63</v>
+        <v>6.62</v>
       </c>
     </row>
   </sheetData>
@@ -31667,7 +31698,7 @@
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>20.48</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="3">
@@ -31678,7 +31709,7 @@
         <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>19.39</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="4">
@@ -31689,7 +31720,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18.08</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="5">
@@ -31697,10 +31728,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>16.99</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="6">
@@ -31711,7 +31742,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.99</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="7">
@@ -31722,7 +31753,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.78</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="8">
@@ -31733,7 +31764,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.56</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="9">
@@ -31744,7 +31775,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>16.12</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="10">
@@ -31755,7 +31786,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.25</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="11">
@@ -31766,7 +31797,7 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>14.81</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="12">
@@ -31774,10 +31805,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
-        <v>14.38</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="13">
@@ -31788,7 +31819,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.16</v>
+        <v>14.13</v>
       </c>
     </row>
   </sheetData>
@@ -31850,7 +31881,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6 &amp; 11</t>
+          <t>15 &amp; 24</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -31860,7 +31891,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6 &amp; 49</t>
+          <t>6 &amp; 11</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -31870,7 +31901,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1 &amp; 7</t>
+          <t>6 &amp; 49</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -31880,7 +31911,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11 &amp; 23</t>
+          <t>1 &amp; 7</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -31890,7 +31921,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21 &amp; 34</t>
+          <t>11 &amp; 23</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -31900,11 +31931,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15 &amp; 24</t>
+          <t>21 &amp; 34</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -32281,184 +32312,184 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B3" t="n">
         <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.81</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B6" t="n">
         <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B13" t="n">
         <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -32466,346 +32497,346 @@
         <v>44</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>10.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B16" t="n">
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B17" t="n">
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>9.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="D21" t="n">
-        <v>0.78</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B22" t="n">
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D22" t="n">
-        <v>1.02</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>12.4</v>
+        <v>9.5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.78</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0.77</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.1</v>
+        <v>8.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="D29" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.48</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="D34" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>8.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="D38" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
         <v>0.22</v>
@@ -32813,13 +32844,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="D40" t="n">
         <v>0.2</v>
@@ -32827,55 +32858,55 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D44" t="n">
         <v>0.1</v>
@@ -32883,27 +32914,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D46" t="n">
         <v>0.11</v>
@@ -32911,13 +32942,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>11.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32925,13 +32956,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -32939,13 +32970,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.4</v>
+        <v>10.9</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32953,13 +32984,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32967,13 +32998,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I983"/>
+  <dimension ref="A1:I984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30913,6 +30913,37 @@
       </c>
       <c r="I983" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>25</v>
+      </c>
+      <c r="D984" t="n">
+        <v>35</v>
+      </c>
+      <c r="E984" t="n">
+        <v>45</v>
+      </c>
+      <c r="F984" t="n">
+        <v>46</v>
+      </c>
+      <c r="G984" t="n">
+        <v>50</v>
+      </c>
+      <c r="H984" t="n">
+        <v>4</v>
+      </c>
+      <c r="I984" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -30954,7 +30985,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.71</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="3">
@@ -30965,7 +30996,7 @@
         <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="4">
@@ -30976,7 +31007,7 @@
         <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="5">
@@ -30984,10 +31015,10 @@
         <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.3</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="6">
@@ -30998,7 +31029,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="7">
@@ -31009,7 +31040,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="8">
@@ -31020,7 +31051,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="9">
@@ -31031,7 +31062,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="10">
@@ -31042,7 +31073,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="11">
@@ -31053,7 +31084,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="12">
@@ -31064,7 +31095,7 @@
         <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="13">
@@ -31075,7 +31106,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="14">
@@ -31086,7 +31117,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="15">
@@ -31097,7 +31128,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.59</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="16">
@@ -31108,7 +31139,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="17">
@@ -31119,29 +31150,29 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B18" t="n">
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.29</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="B19" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" t="n">
-        <v>10.18</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="20">
@@ -31152,7 +31183,7 @@
         <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="21">
@@ -31163,51 +31194,51 @@
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B22" t="n">
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B24" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.08</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B25" t="n">
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="26">
@@ -31218,7 +31249,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="27">
@@ -31229,7 +31260,7 @@
         <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -31240,7 +31271,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -31251,7 +31282,7 @@
         <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -31262,7 +31293,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -31273,7 +31304,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="32">
@@ -31284,7 +31315,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="33">
@@ -31295,7 +31326,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="34">
@@ -31306,7 +31337,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="35">
@@ -31317,7 +31348,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="36">
@@ -31328,7 +31359,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -31339,7 +31370,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31350,7 +31381,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31361,7 +31392,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -31372,7 +31403,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -31383,7 +31414,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -31394,7 +31425,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.27</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="43">
@@ -31427,62 +31458,62 @@
         <v>87</v>
       </c>
       <c r="C45" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46" t="n">
         <v>87</v>
       </c>
       <c r="C46" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B47" t="n">
         <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C49" t="n">
-        <v>8.66</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B50" t="n">
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="51">
@@ -31493,7 +31524,7 @@
         <v>78</v>
       </c>
       <c r="C51" t="n">
-        <v>7.94</v>
+        <v>7.93</v>
       </c>
     </row>
   </sheetData>
@@ -31535,7 +31566,7 @@
         <v>211</v>
       </c>
       <c r="C2" t="n">
-        <v>21.49</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="3">
@@ -31546,7 +31577,7 @@
         <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>20.37</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="4">
@@ -31554,10 +31585,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.76</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="5">
@@ -31568,29 +31599,29 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>19.45</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
         <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>18.64</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.53</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="8">
@@ -31601,7 +31632,7 @@
         <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.13</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="9">
@@ -31612,7 +31643,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>17.01</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="10">
@@ -31623,7 +31654,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.6</v>
+        <v>16.58</v>
       </c>
     </row>
     <row r="11">
@@ -31634,7 +31665,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.97</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="12">
@@ -31645,7 +31676,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.449999999999999</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="13">
@@ -31656,7 +31687,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.62</v>
+        <v>6.61</v>
       </c>
     </row>
   </sheetData>
@@ -31698,7 +31729,7 @@
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>20.43</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="3">
@@ -31709,7 +31740,7 @@
         <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>19.35</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="4">
@@ -31720,7 +31751,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18.04</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -31731,7 +31762,7 @@
         <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>17.17</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="6">
@@ -31742,7 +31773,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.96</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="7">
@@ -31753,7 +31784,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.74</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="8">
@@ -31764,7 +31795,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.52</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="9">
@@ -31775,7 +31806,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>16.09</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="10">
@@ -31786,7 +31817,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.22</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="11">
@@ -31794,10 +31825,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" t="n">
-        <v>14.78</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="12">
@@ -31805,10 +31836,10 @@
         <v>4</v>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" t="n">
-        <v>14.57</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="13">
@@ -31819,7 +31850,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.13</v>
+        <v>14.1</v>
       </c>
     </row>
   </sheetData>
@@ -32001,17 +32032,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>35 &amp; 46</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -32021,7 +32052,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -32031,7 +32062,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -32041,7 +32072,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32051,7 +32082,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26 &amp; 49</t>
+          <t>20 &amp; 49</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32061,7 +32092,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2 &amp; 21</t>
+          <t>26 &amp; 49</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -32071,7 +32102,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11 &amp; 35</t>
+          <t>2 &amp; 21</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32081,7 +32112,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30 &amp; 43</t>
+          <t>11 &amp; 35</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32091,7 +32122,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1 &amp; 47</t>
+          <t>30 &amp; 43</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32315,13 +32346,13 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
         <v>9.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="3">
@@ -32329,13 +32360,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>10.3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="4">
@@ -32343,13 +32374,13 @@
         <v>33</v>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>10.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="5">
@@ -32357,13 +32388,13 @@
         <v>49</v>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="6">
@@ -32371,13 +32402,13 @@
         <v>38</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>9.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -32385,13 +32416,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>10.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="8">
@@ -32399,13 +32430,13 @@
         <v>18</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="9">
@@ -32413,13 +32444,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="10">
@@ -32427,13 +32458,13 @@
         <v>29</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>10.1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="11">
@@ -32441,13 +32472,13 @@
         <v>27</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>11.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="12">
@@ -32455,13 +32486,13 @@
         <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>9.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -32469,304 +32500,304 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>9.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.35</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D17" t="n">
-        <v>1.23</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="D20" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>1.01</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D23" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>11.3</v>
+        <v>8.4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>8.4</v>
+        <v>9.9</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>10.8</v>
+        <v>9.1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
         <v>0.3</v>
@@ -32774,181 +32805,181 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>9.199999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>11.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>11.4</v>
+        <v>10.1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.4</v>
+        <v>10.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32956,7 +32987,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
@@ -32970,13 +33001,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -32984,13 +33015,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -32998,13 +33029,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I984"/>
+  <dimension ref="A1:I985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30944,6 +30944,37 @@
       </c>
       <c r="I984" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>4</v>
+      </c>
+      <c r="D985" t="n">
+        <v>5</v>
+      </c>
+      <c r="E985" t="n">
+        <v>7</v>
+      </c>
+      <c r="F985" t="n">
+        <v>48</v>
+      </c>
+      <c r="G985" t="n">
+        <v>50</v>
+      </c>
+      <c r="H985" t="n">
+        <v>4</v>
+      </c>
+      <c r="I985" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -30985,7 +31016,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.7</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="3">
@@ -30996,7 +31027,7 @@
         <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="4">
@@ -31007,7 +31038,7 @@
         <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="5">
@@ -31018,7 +31049,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="6">
@@ -31029,7 +31060,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="7">
@@ -31040,7 +31071,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="8">
@@ -31051,7 +31082,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="9">
@@ -31062,7 +31093,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.89</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="10">
@@ -31073,7 +31104,7 @@
         <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="11">
@@ -31084,7 +31115,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="12">
@@ -31095,7 +31126,7 @@
         <v>105</v>
       </c>
       <c r="C12" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="13">
@@ -31106,7 +31137,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="14">
@@ -31117,7 +31148,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="15">
@@ -31128,7 +31159,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="16">
@@ -31139,7 +31170,7 @@
         <v>103</v>
       </c>
       <c r="C16" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="17">
@@ -31150,7 +31181,7 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="18">
@@ -31161,51 +31192,51 @@
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B19" t="n">
         <v>101</v>
       </c>
       <c r="C19" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B20" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.17</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B21" t="n">
         <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B22" t="n">
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="23">
@@ -31216,7 +31247,7 @@
         <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="24">
@@ -31227,7 +31258,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="25">
@@ -31238,29 +31269,29 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B27" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>9.970000000000001</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="28">
@@ -31271,7 +31302,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -31282,7 +31313,7 @@
         <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.869999999999999</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -31293,7 +31324,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.869999999999999</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -31304,7 +31335,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="32">
@@ -31315,7 +31346,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="33">
@@ -31326,7 +31357,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="34">
@@ -31337,7 +31368,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="35">
@@ -31348,7 +31379,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -31359,7 +31390,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -31370,7 +31401,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -31381,7 +31412,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -31392,7 +31423,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -31403,7 +31434,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="41">
@@ -31414,7 +31445,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="42">
@@ -31425,7 +31456,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.26</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="43">
@@ -31436,7 +31467,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="44">
@@ -31447,7 +31478,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="45">
@@ -31455,10 +31486,10 @@
         <v>5</v>
       </c>
       <c r="B45" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C45" t="n">
-        <v>8.85</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="46">
@@ -31469,7 +31500,7 @@
         <v>87</v>
       </c>
       <c r="C46" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="47">
@@ -31480,7 +31511,7 @@
         <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="48">
@@ -31491,7 +31522,7 @@
         <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="49">
@@ -31499,10 +31530,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.75</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="50">
@@ -31513,7 +31544,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -31521,10 +31552,10 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>7.93</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -31563,10 +31594,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.46</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="3">
@@ -31577,7 +31608,7 @@
         <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="4">
@@ -31588,7 +31619,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.84</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="5">
@@ -31599,7 +31630,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>19.43</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="6">
@@ -31607,10 +31638,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C6" t="n">
-        <v>18.62</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="7">
@@ -31621,7 +31652,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.62</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="8">
@@ -31632,7 +31663,7 @@
         <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>18.11</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="9">
@@ -31643,7 +31674,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.99</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="10">
@@ -31654,7 +31685,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.58</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="11">
@@ -31665,7 +31696,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.95</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="12">
@@ -31676,7 +31707,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.44</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="13">
@@ -31726,10 +31757,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.39</v>
+        <v>20.56</v>
       </c>
     </row>
     <row r="3">
@@ -31740,7 +31771,7 @@
         <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>19.31</v>
+        <v>19.26</v>
       </c>
     </row>
     <row r="4">
@@ -31751,7 +31782,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="5">
@@ -31762,7 +31793,7 @@
         <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>17.14</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6">
@@ -31773,7 +31804,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.92</v>
+        <v>16.88</v>
       </c>
     </row>
     <row r="7">
@@ -31784,7 +31815,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="8">
@@ -31795,7 +31826,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.49</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="9">
@@ -31806,7 +31837,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>16.05</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="10">
@@ -31817,29 +31848,29 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.18</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11" t="n">
         <v>69</v>
       </c>
       <c r="C11" t="n">
-        <v>14.97</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="13">
@@ -31850,7 +31881,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.1</v>
+        <v>14.07</v>
       </c>
     </row>
   </sheetData>
@@ -32343,212 +32374,212 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.71</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B4" t="n">
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B5" t="n">
         <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.99</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="D8" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" t="n">
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="B11" t="n">
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B16" t="n">
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="D16" t="n">
-        <v>0.95</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="17">
@@ -32556,304 +32587,304 @@
         <v>47</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>10.3</v>
       </c>
       <c r="D17" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>10.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.12</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D21" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="D29" t="n">
-        <v>0.44</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.43</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
         <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>11.4</v>
+        <v>9.4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D38" t="n">
         <v>0.18</v>
@@ -32861,125 +32892,125 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -32987,13 +33018,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33001,7 +33032,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -33015,13 +33046,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33035,7 +33066,7 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I985"/>
+  <dimension ref="A1:I986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30975,6 +30975,37 @@
       </c>
       <c r="I985" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>23</v>
+      </c>
+      <c r="D986" t="n">
+        <v>34</v>
+      </c>
+      <c r="E986" t="n">
+        <v>39</v>
+      </c>
+      <c r="F986" t="n">
+        <v>45</v>
+      </c>
+      <c r="G986" t="n">
+        <v>49</v>
+      </c>
+      <c r="H986" t="n">
+        <v>1</v>
+      </c>
+      <c r="I986" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -31016,29 +31047,29 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.69</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" t="n">
-        <v>11.38</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B4" t="n">
         <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="5">
@@ -31049,7 +31080,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="6">
@@ -31060,7 +31091,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="7">
@@ -31071,7 +31102,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="8">
@@ -31082,7 +31113,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.08</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="9">
@@ -31093,7 +31124,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.87</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="10">
@@ -31101,10 +31132,10 @@
         <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.77</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="11">
@@ -31115,7 +31146,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.77</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="12">
@@ -31123,10 +31154,10 @@
         <v>23</v>
       </c>
       <c r="B12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.67</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="13">
@@ -31137,7 +31168,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="14">
@@ -31148,7 +31179,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="15">
@@ -31159,40 +31190,40 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B16" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.47</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B18" t="n">
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="19">
@@ -31203,29 +31234,29 @@
         <v>101</v>
       </c>
       <c r="C19" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.16</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="22">
@@ -31236,18 +31267,18 @@
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="B23" t="n">
         <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="24">
@@ -31258,7 +31289,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="25">
@@ -31269,7 +31300,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="26">
@@ -31280,7 +31311,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="27">
@@ -31291,7 +31322,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="28">
@@ -31302,7 +31333,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -31313,7 +31344,7 @@
         <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="30">
@@ -31324,7 +31355,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="31">
@@ -31335,7 +31366,7 @@
         <v>96</v>
       </c>
       <c r="C31" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="32">
@@ -31346,7 +31377,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="33">
@@ -31357,7 +31388,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="34">
@@ -31368,7 +31399,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.65</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31379,7 +31410,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -31390,7 +31421,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="37">
@@ -31401,7 +31432,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="38">
@@ -31412,7 +31443,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="39">
@@ -31423,7 +31454,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="40">
@@ -31434,7 +31465,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="41">
@@ -31445,7 +31476,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="42">
@@ -31456,7 +31487,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="43">
@@ -31467,7 +31498,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -31478,7 +31509,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.15</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -31489,7 +31520,7 @@
         <v>88</v>
       </c>
       <c r="C45" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="46">
@@ -31500,7 +31531,7 @@
         <v>87</v>
       </c>
       <c r="C46" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="47">
@@ -31511,7 +31542,7 @@
         <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="48">
@@ -31522,7 +31553,7 @@
         <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="49">
@@ -31533,7 +31564,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="50">
@@ -31544,7 +31575,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -31555,7 +31586,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
     </row>
   </sheetData>
@@ -31597,7 +31628,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.54</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="3">
@@ -31608,7 +31639,7 @@
         <v>200</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4">
@@ -31619,7 +31650,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.82</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="5">
@@ -31630,7 +31661,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>19.41</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="6">
@@ -31638,10 +31669,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>18.7</v>
+        <v>18.78</v>
       </c>
     </row>
     <row r="7">
@@ -31652,7 +31683,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.6</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="8">
@@ -31660,10 +31691,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>18.09</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="9">
@@ -31674,7 +31705,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.97</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="10">
@@ -31685,7 +31716,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.57</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="11">
@@ -31696,7 +31727,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.94</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="12">
@@ -31718,7 +31749,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.61</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -31760,7 +31791,7 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.56</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="3">
@@ -31771,7 +31802,7 @@
         <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>19.26</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="4">
@@ -31782,7 +31813,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>17.97</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="5">
@@ -31793,29 +31824,29 @@
         <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>17.1</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.88</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.67</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="8">
@@ -31826,7 +31857,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.45</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="9">
@@ -31837,29 +31868,29 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>16.02</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" t="n">
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.15</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.94</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="12">
@@ -31870,7 +31901,7 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>14.94</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="13">
@@ -31881,7 +31912,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.07</v>
+        <v>14.04</v>
       </c>
     </row>
   </sheetData>
@@ -31917,7 +31948,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -32377,13 +32408,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
         <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
@@ -32391,41 +32422,41 @@
         <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
         <v>10.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B4" t="n">
         <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="D5" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
@@ -32433,13 +32464,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="7">
@@ -32447,164 +32478,164 @@
         <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B8" t="n">
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B12" t="n">
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>10.4</v>
+        <v>11.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B15" t="n">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>11.5</v>
+        <v>10.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B17" t="n">
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D18" t="n">
         <v>1.06</v>
@@ -32612,100 +32643,100 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D19" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>41</v>
+      </c>
+      <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="B20" t="n">
-        <v>9</v>
-      </c>
       <c r="C20" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.65</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.76</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D24" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="26">
@@ -32713,38 +32744,38 @@
         <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
         <v>9.1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D28" t="n">
         <v>0.49</v>
@@ -32752,175 +32783,175 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D29" t="n">
-        <v>0.51</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>0.52</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="D32" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.27</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D36" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.4</v>
+        <v>10.9</v>
       </c>
       <c r="D37" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
@@ -32934,83 +32965,83 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>8.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33018,13 +33049,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>11.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33032,13 +33063,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33046,13 +33077,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33060,13 +33091,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>11.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I986"/>
+  <dimension ref="A1:I987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31006,6 +31006,37 @@
       </c>
       <c r="I986" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>9</v>
+      </c>
+      <c r="D987" t="n">
+        <v>14</v>
+      </c>
+      <c r="E987" t="n">
+        <v>35</v>
+      </c>
+      <c r="F987" t="n">
+        <v>43</v>
+      </c>
+      <c r="G987" t="n">
+        <v>50</v>
+      </c>
+      <c r="H987" t="n">
+        <v>3</v>
+      </c>
+      <c r="I987" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -31047,7 +31078,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.68</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="3">
@@ -31058,29 +31089,29 @@
         <v>113</v>
       </c>
       <c r="C3" t="n">
-        <v>11.47</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" t="n">
-        <v>11.37</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B5" t="n">
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.37</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="6">
@@ -31091,7 +31122,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="7">
@@ -31102,7 +31133,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.17</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="8">
@@ -31113,7 +31144,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.07</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="9">
@@ -31124,7 +31155,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.86</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="10">
@@ -31135,7 +31166,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.86</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="11">
@@ -31146,7 +31177,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="12">
@@ -31157,7 +31188,7 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="13">
@@ -31168,7 +31199,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="14">
@@ -31179,7 +31210,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="15">
@@ -31190,7 +31221,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="16">
@@ -31201,7 +31232,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="17">
@@ -31212,84 +31243,84 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B18" t="n">
         <v>101</v>
       </c>
       <c r="C18" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
         <v>101</v>
       </c>
       <c r="C19" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B20" t="n">
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B21" t="n">
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.15</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B23" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.15</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" t="n">
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="25">
@@ -31300,7 +31331,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="26">
@@ -31311,7 +31342,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="27">
@@ -31322,7 +31353,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="28">
@@ -31333,7 +31364,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="29">
@@ -31344,7 +31375,7 @@
         <v>97</v>
       </c>
       <c r="C29" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="30">
@@ -31355,40 +31386,40 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B31" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.75</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B32" t="n">
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B33" t="n">
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="34">
@@ -31399,7 +31430,7 @@
         <v>95</v>
       </c>
       <c r="C34" t="n">
-        <v>9.640000000000001</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31410,7 +31441,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -31421,7 +31452,7 @@
         <v>93</v>
       </c>
       <c r="C36" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="37">
@@ -31432,7 +31463,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="38">
@@ -31443,7 +31474,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="39">
@@ -31454,7 +31485,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="40">
@@ -31465,7 +31496,7 @@
         <v>92</v>
       </c>
       <c r="C40" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="41">
@@ -31476,7 +31507,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="42">
@@ -31487,7 +31518,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.24</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="43">
@@ -31498,7 +31529,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -31509,7 +31540,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.140000000000001</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -31520,29 +31551,29 @@
         <v>88</v>
       </c>
       <c r="C45" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B46" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C46" t="n">
-        <v>8.83</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B47" t="n">
         <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="48">
@@ -31553,18 +31584,18 @@
         <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B49" t="n">
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="50">
@@ -31575,7 +31606,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -31586,7 +31617,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>8.02</v>
+        <v>8.01</v>
       </c>
     </row>
   </sheetData>
@@ -31628,7 +31659,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.52</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="3">
@@ -31636,10 +31667,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C3" t="n">
-        <v>20.3</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="4">
@@ -31650,7 +31681,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="5">
@@ -31658,10 +31689,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.39</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="6">
@@ -31672,7 +31703,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>18.78</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="7">
@@ -31683,7 +31714,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.58</v>
+        <v>18.56</v>
       </c>
     </row>
     <row r="8">
@@ -31694,7 +31725,7 @@
         <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>18.17</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="9">
@@ -31705,7 +31736,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.95</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="10">
@@ -31716,7 +31747,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.55</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="11">
@@ -31727,7 +31758,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.92</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="12">
@@ -31738,7 +31769,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.43</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="13">
@@ -31749,7 +31780,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.6</v>
+        <v>6.59</v>
       </c>
     </row>
   </sheetData>
@@ -31791,7 +31822,7 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.52</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="3">
@@ -31799,10 +31830,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" t="n">
-        <v>19.22</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="4">
@@ -31813,7 +31844,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>17.93</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="5">
@@ -31821,10 +31852,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.06</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="6">
@@ -31835,7 +31866,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.85</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="7">
@@ -31846,7 +31877,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.85</v>
+        <v>16.81</v>
       </c>
     </row>
     <row r="8">
@@ -31857,7 +31888,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.41</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="9">
@@ -31868,7 +31899,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.98</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="10">
@@ -31879,7 +31910,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>15.12</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="11">
@@ -31890,7 +31921,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>15.12</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="12">
@@ -31901,7 +31932,7 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>14.9</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="13">
@@ -31912,7 +31943,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04</v>
+        <v>14.01</v>
       </c>
     </row>
   </sheetData>
@@ -32408,13 +32439,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
         <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -32422,13 +32453,13 @@
         <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>10.4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -32436,346 +32467,346 @@
         <v>38</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>9.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.19</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B7" t="n">
         <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>10.4</v>
+        <v>11.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="D14" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B15" t="n">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D17" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.96</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>8.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="D24" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9.1</v>
+        <v>10.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D28" t="n">
         <v>0.49</v>
@@ -32783,161 +32814,161 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>9.800000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="D38" t="n">
-        <v>0.28</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
@@ -32951,97 +32982,97 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>8.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>11.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>12.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33049,13 +33080,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33063,13 +33094,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33077,13 +33108,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33091,13 +33122,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I987"/>
+  <dimension ref="A1:I988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31037,6 +31037,37 @@
       </c>
       <c r="I987" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>5</v>
+      </c>
+      <c r="D988" t="n">
+        <v>14</v>
+      </c>
+      <c r="E988" t="n">
+        <v>31</v>
+      </c>
+      <c r="F988" t="n">
+        <v>33</v>
+      </c>
+      <c r="G988" t="n">
+        <v>43</v>
+      </c>
+      <c r="H988" t="n">
+        <v>3</v>
+      </c>
+      <c r="I988" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -31078,7 +31109,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.66</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="3">
@@ -31089,7 +31120,7 @@
         <v>113</v>
       </c>
       <c r="C3" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="4">
@@ -31100,7 +31131,7 @@
         <v>113</v>
       </c>
       <c r="C4" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="5">
@@ -31111,7 +31142,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.36</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="6">
@@ -31122,7 +31153,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.16</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="7">
@@ -31133,7 +31164,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.16</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="8">
@@ -31144,7 +31175,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="9">
@@ -31155,7 +31186,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="10">
@@ -31166,7 +31197,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="11">
@@ -31177,7 +31208,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.75</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="12">
@@ -31188,7 +31219,7 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.75</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="13">
@@ -31199,7 +31230,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.65</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="14">
@@ -31210,7 +31241,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.65</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="15">
@@ -31221,7 +31252,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.55</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="16">
@@ -31232,7 +31263,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.55</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="17">
@@ -31243,29 +31274,29 @@
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B18" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" t="n">
-        <v>10.24</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
         <v>101</v>
       </c>
       <c r="C19" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="20">
@@ -31276,7 +31307,7 @@
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="21">
@@ -31287,7 +31318,7 @@
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="22">
@@ -31298,7 +31329,7 @@
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="23">
@@ -31309,7 +31340,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="24">
@@ -31320,7 +31351,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="25">
@@ -31331,7 +31362,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="26">
@@ -31342,7 +31373,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="27">
@@ -31353,51 +31384,51 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B29" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.84</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B30" t="n">
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B31" t="n">
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="32">
@@ -31408,7 +31439,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="33">
@@ -31419,7 +31450,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="34">
@@ -31441,7 +31472,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="36">
@@ -31449,10 +31480,10 @@
         <v>31</v>
       </c>
       <c r="B36" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.43</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="37">
@@ -31463,7 +31494,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="38">
@@ -31474,40 +31505,40 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B39" t="n">
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.33</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B41" t="n">
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="42">
@@ -31518,7 +31549,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -31529,7 +31560,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.130000000000001</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -31540,7 +31571,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.130000000000001</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -31548,10 +31579,10 @@
         <v>5</v>
       </c>
       <c r="B45" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" t="n">
-        <v>8.92</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="46">
@@ -31573,7 +31604,7 @@
         <v>87</v>
       </c>
       <c r="C47" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="48">
@@ -31584,7 +31615,7 @@
         <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="49">
@@ -31595,7 +31626,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="50">
@@ -31606,7 +31637,7 @@
         <v>85</v>
       </c>
       <c r="C50" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -31617,7 +31648,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -31659,7 +31690,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="3">
@@ -31667,10 +31698,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="4">
@@ -31681,7 +31712,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.78</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="5">
@@ -31692,7 +31723,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.47</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="6">
@@ -31700,10 +31731,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C6" t="n">
-        <v>18.76</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="7">
@@ -31714,7 +31745,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.56</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="8">
@@ -31725,7 +31756,7 @@
         <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="9">
@@ -31736,7 +31767,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.94</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="10">
@@ -31747,7 +31778,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.53</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="11">
@@ -31758,7 +31789,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="12">
@@ -31769,7 +31800,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.42</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="13">
@@ -31822,7 +31853,7 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.47</v>
+        <v>20.43</v>
       </c>
     </row>
     <row r="3">
@@ -31830,10 +31861,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
-        <v>19.4</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="4">
@@ -31844,7 +31875,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>17.89</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="5">
@@ -31855,7 +31886,7 @@
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.24</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="6">
@@ -31866,7 +31897,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.81</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="7">
@@ -31877,7 +31908,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.81</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="8">
@@ -31888,7 +31919,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.38</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="9">
@@ -31899,7 +31930,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.95</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="10">
@@ -31907,10 +31938,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>15.09</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="11">
@@ -31921,7 +31952,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>15.09</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="12">
@@ -31932,7 +31963,7 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>14.87</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="13">
@@ -31943,7 +31974,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>14.01</v>
+        <v>13.98</v>
       </c>
     </row>
   </sheetData>
@@ -32439,178 +32470,178 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
         <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B6" t="n">
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B9" t="n">
         <v>19</v>
       </c>
-      <c r="B9" t="n">
-        <v>18</v>
-      </c>
       <c r="C9" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>10.4</v>
+        <v>11.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="D12" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>10.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D14" t="n">
         <v>1.27</v>
@@ -32618,240 +32649,240 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>41</v>
+      </c>
+      <c r="B17" t="n">
         <v>10</v>
       </c>
-      <c r="B17" t="n">
-        <v>9</v>
-      </c>
       <c r="C17" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B18" t="n">
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="D21" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B24" t="n">
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
         <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0.67</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D27" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="D31" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="32">
@@ -32859,13 +32890,13 @@
         <v>42</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
         <v>10.6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="33">
@@ -32873,102 +32904,102 @@
         <v>15</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>11.3</v>
+        <v>9.9</v>
       </c>
       <c r="D38" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
@@ -32982,16 +33013,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>12.3</v>
+        <v>9.5</v>
       </c>
       <c r="D41" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42">
@@ -32999,13 +33030,13 @@
         <v>34</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="43">
@@ -33013,38 +33044,38 @@
         <v>23</v>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D45" t="n">
         <v>0.11</v>
@@ -33052,27 +33083,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33086,7 +33117,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33094,13 +33125,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33108,13 +33139,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33122,13 +33153,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
